--- a/pregenereated_results/s2/ate_iptw_gee_IPTW_GEE_turnover_intention_index_mgr.xlsx
+++ b/pregenereated_results/s2/ate_iptw_gee_IPTW_GEE_turnover_intention_index_mgr.xlsx
@@ -1388,7 +1388,7 @@
         <v>7220</v>
       </c>
       <c r="B2" t="n">
-        <v>7094.386718944054</v>
+        <v>7094.386718944053</v>
       </c>
       <c r="C2" t="n">
         <v>0.9957648995493169</v>
@@ -1397,13 +1397,13 @@
         <v>0.1325095691671194</v>
       </c>
       <c r="E2" t="n">
-        <v>1.678870188120528</v>
+        <v>1.678870188120527</v>
       </c>
       <c r="F2" t="n">
         <v>1.124267686541995</v>
       </c>
       <c r="G2" t="n">
-        <v>1.67804342107184</v>
+        <v>1.678043421071839</v>
       </c>
     </row>
   </sheetData>
@@ -1464,19 +1464,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.588437647332136</v>
+        <v>1.588437647332135</v>
       </c>
       <c r="C2" t="n">
-        <v>0.09951383604477247</v>
+        <v>0.09951383604476918</v>
       </c>
       <c r="D2" t="n">
-        <v>1.393394112720958</v>
+        <v>1.393394112720964</v>
       </c>
       <c r="E2" t="n">
-        <v>1.783481181943314</v>
+        <v>1.783481181943307</v>
       </c>
       <c r="F2" t="n">
-        <v>2.351594952938109e-57</v>
+        <v>2.351594952918417e-57</v>
       </c>
       <c r="G2" t="n">
         <v>0.05</v>
@@ -1489,19 +1489,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.002289543090502408</v>
+        <v>0.002289543090502453</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0200435016019184</v>
+        <v>0.02004350160191842</v>
       </c>
       <c r="D3" t="n">
         <v>-0.03699499817332853</v>
       </c>
       <c r="E3" t="n">
-        <v>0.04157408435433335</v>
+        <v>0.04157408435433343</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9090565031154852</v>
+        <v>0.9090565031154836</v>
       </c>
       <c r="G3" t="n">
         <v>0.05</v>
@@ -1514,16 +1514,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.02760529193760395</v>
+        <v>-0.02760529193760394</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0518165195556562</v>
+        <v>0.05181651955565619</v>
       </c>
       <c r="D4" t="n">
         <v>-0.1291638040709055</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0739532201956976</v>
+        <v>0.07395322019569761</v>
       </c>
       <c r="F4" t="n">
         <v>0.5942060998044847</v>
@@ -1539,19 +1539,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.001979053634585209</v>
+        <v>0.001979053634585241</v>
       </c>
       <c r="C5" t="n">
         <v>0.03523203519821221</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.06707446645595823</v>
+        <v>-0.06707446645595819</v>
       </c>
       <c r="E5" t="n">
-        <v>0.07103257372512865</v>
+        <v>0.07103257372512867</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9552047922717004</v>
+        <v>0.9552047922716996</v>
       </c>
       <c r="G5" t="n">
         <v>0.05</v>
@@ -1564,19 +1564,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03340001985125</v>
+        <v>0.03340001985125003</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0328625850817722</v>
+        <v>0.03286258508177218</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.03100946334790678</v>
+        <v>-0.0310094633479067</v>
       </c>
       <c r="E6" t="n">
-        <v>0.09780950305040678</v>
+        <v>0.09780950305040677</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3094608416342981</v>
+        <v>0.3094608416342971</v>
       </c>
       <c r="G6" t="n">
         <v>0.05</v>
@@ -1589,19 +1589,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.01514663535578092</v>
+        <v>-0.01514663535578087</v>
       </c>
       <c r="C7" t="n">
-        <v>0.03537760492293866</v>
+        <v>0.03537760492293865</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.08448546686402761</v>
+        <v>-0.08448546686402754</v>
       </c>
       <c r="E7" t="n">
-        <v>0.05419219615246578</v>
+        <v>0.0541921961524658</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6685478054594487</v>
+        <v>0.6685478054594496</v>
       </c>
       <c r="G7" t="n">
         <v>0.05</v>
@@ -1614,19 +1614,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.01391452100577122</v>
+        <v>-0.01391452100577118</v>
       </c>
       <c r="C8" t="n">
-        <v>0.03582624135777856</v>
+        <v>0.03582624135777854</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.08413266376845656</v>
+        <v>-0.08413266376845648</v>
       </c>
       <c r="E8" t="n">
         <v>0.05630362175691413</v>
       </c>
       <c r="F8" t="n">
-        <v>0.697728122369965</v>
+        <v>0.6977281223699656</v>
       </c>
       <c r="G8" t="n">
         <v>0.05</v>
@@ -1639,19 +1639,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.02606854715545239</v>
+        <v>-0.02606854715545236</v>
       </c>
       <c r="C9" t="n">
-        <v>0.03445174256130683</v>
+        <v>0.03445174256130681</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.09359272178025949</v>
+        <v>-0.09359272178025943</v>
       </c>
       <c r="E9" t="n">
-        <v>0.04145562746935472</v>
+        <v>0.04145562746935471</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4492485122499703</v>
+        <v>0.4492485122499706</v>
       </c>
       <c r="G9" t="n">
         <v>0.05</v>
@@ -1667,16 +1667,16 @@
         <v>-0.1243555105431011</v>
       </c>
       <c r="C10" t="n">
-        <v>0.05548145045815731</v>
+        <v>0.05548145045815717</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.2330971552511327</v>
+        <v>-0.2330971552511324</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.01561386583506946</v>
+        <v>-0.01561386583506978</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0250008910074542</v>
+        <v>0.02500089100745381</v>
       </c>
       <c r="G10" t="n">
         <v>0.05</v>
@@ -1692,16 +1692,16 @@
         <v>0.07368505338474868</v>
       </c>
       <c r="C11" t="n">
-        <v>0.05628990533964618</v>
+        <v>0.05628990533964612</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.03664113377412671</v>
+        <v>-0.03664113377412659</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1840112405436241</v>
+        <v>0.1840112405436239</v>
       </c>
       <c r="F11" t="n">
-        <v>0.190524919365661</v>
+        <v>0.1905249193656604</v>
       </c>
       <c r="G11" t="n">
         <v>0.05</v>
@@ -1714,19 +1714,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.0603922635557704</v>
+        <v>-0.06039226355577043</v>
       </c>
       <c r="C12" t="n">
-        <v>0.06009378790448151</v>
+        <v>0.06009378790448146</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.1781739235431429</v>
+        <v>-0.1781739235431428</v>
       </c>
       <c r="E12" t="n">
-        <v>0.05738939643160208</v>
+        <v>0.05738939643160196</v>
       </c>
       <c r="F12" t="n">
-        <v>0.3149128220217325</v>
+        <v>0.3149128220217319</v>
       </c>
       <c r="G12" t="n">
         <v>0.05</v>
@@ -1739,19 +1739,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.03918292931079818</v>
+        <v>-0.03918292931079817</v>
       </c>
       <c r="C13" t="n">
-        <v>0.05709010836228827</v>
+        <v>0.05709010836228823</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.1510774855743722</v>
+        <v>-0.1510774855743721</v>
       </c>
       <c r="E13" t="n">
-        <v>0.07271162695277579</v>
+        <v>0.07271162695277572</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4925019956822239</v>
+        <v>0.4925019956822237</v>
       </c>
       <c r="G13" t="n">
         <v>0.05</v>
@@ -1764,19 +1764,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.08961924675638726</v>
+        <v>-0.08961924675638717</v>
       </c>
       <c r="C14" t="n">
         <v>0.05597301997478087</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.1993243500128988</v>
+        <v>-0.1993243500128987</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0200858565001243</v>
+        <v>0.02008585650012439</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1093514311924689</v>
+        <v>0.1093514311924692</v>
       </c>
       <c r="G14" t="n">
         <v>0.05</v>
@@ -1789,19 +1789,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.07971063832368426</v>
+        <v>-0.07971063832368429</v>
       </c>
       <c r="C15" t="n">
-        <v>0.05486702563238855</v>
+        <v>0.05486702563238852</v>
       </c>
       <c r="D15" t="n">
         <v>-0.1872480325020018</v>
       </c>
       <c r="E15" t="n">
-        <v>0.02782675585463329</v>
+        <v>0.02782675585463319</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1462801854677673</v>
+        <v>0.146280185467767</v>
       </c>
       <c r="G15" t="n">
         <v>0.05</v>
@@ -1814,19 +1814,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.07536173463392259</v>
+        <v>-0.07536173463392262</v>
       </c>
       <c r="C16" t="n">
-        <v>0.05394309282729044</v>
+        <v>0.05394309282729035</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1810882537901128</v>
+        <v>-0.1810882537901126</v>
       </c>
       <c r="E16" t="n">
-        <v>0.03036478452226758</v>
+        <v>0.03036478452226737</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1623955437074909</v>
+        <v>0.16239554370749</v>
       </c>
       <c r="G16" t="n">
         <v>0.05</v>
@@ -1839,19 +1839,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.007508945504431082</v>
+        <v>-0.007508945504431017</v>
       </c>
       <c r="C17" t="n">
-        <v>0.05689726041689014</v>
+        <v>0.05689726041689017</v>
       </c>
       <c r="D17" t="n">
         <v>-0.1190255267405322</v>
       </c>
       <c r="E17" t="n">
-        <v>0.10400763573167</v>
+        <v>0.1040076357316701</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8950050450910969</v>
+        <v>0.8950050450910978</v>
       </c>
       <c r="G17" t="n">
         <v>0.05</v>
@@ -1864,19 +1864,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.02702123264755603</v>
+        <v>-0.02702123264755605</v>
       </c>
       <c r="C18" t="n">
-        <v>0.05498884081168762</v>
+        <v>0.05498884081168755</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.13479738019007</v>
+        <v>-0.1347973801900699</v>
       </c>
       <c r="E18" t="n">
-        <v>0.08075491489495798</v>
+        <v>0.08075491489495783</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6231472128909774</v>
+        <v>0.6231472128909767</v>
       </c>
       <c r="G18" t="n">
         <v>0.05</v>
@@ -1889,19 +1889,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.08375751060329227</v>
+        <v>-0.08375751060329222</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0536099023493513</v>
+        <v>0.05360990234935124</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1888309884227301</v>
+        <v>-0.1888309884227299</v>
       </c>
       <c r="E19" t="n">
-        <v>0.02131596721614551</v>
+        <v>0.02131596721614544</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1182052092143459</v>
+        <v>0.1182052092143456</v>
       </c>
       <c r="G19" t="n">
         <v>0.05</v>
@@ -1914,19 +1914,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.1311358803541574</v>
+        <v>-0.1311358803541575</v>
       </c>
       <c r="C20" t="n">
-        <v>0.05406282801340161</v>
+        <v>0.05406282801340159</v>
       </c>
       <c r="D20" t="n">
         <v>-0.2370970761628077</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.02517468454550713</v>
+        <v>-0.02517468454550724</v>
       </c>
       <c r="F20" t="n">
-        <v>0.01528225980615046</v>
+        <v>0.01528225980615037</v>
       </c>
       <c r="G20" t="n">
         <v>0.05</v>
@@ -1942,16 +1942,16 @@
         <v>-0.1241875106822867</v>
       </c>
       <c r="C21" t="n">
-        <v>0.05616362862747461</v>
+        <v>0.05616362862747459</v>
       </c>
       <c r="D21" t="n">
         <v>-0.2342662000332196</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.01410882133135367</v>
+        <v>-0.01410882133135373</v>
       </c>
       <c r="F21" t="n">
-        <v>0.02702384518809467</v>
+        <v>0.0270238451880946</v>
       </c>
       <c r="G21" t="n">
         <v>0.05</v>
@@ -1964,19 +1964,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.07269691488818501</v>
+        <v>-0.07269691488818499</v>
       </c>
       <c r="C22" t="n">
-        <v>0.05654139166683259</v>
+        <v>0.05654139166683255</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.18351600619095</v>
+        <v>-0.1835160061909499</v>
       </c>
       <c r="E22" t="n">
-        <v>0.03812217641457999</v>
+        <v>0.03812217641457995</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1985376076796671</v>
+        <v>0.198537607679667</v>
       </c>
       <c r="G22" t="n">
         <v>0.05</v>
@@ -1989,19 +1989,19 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.01550704881921868</v>
+        <v>-0.01550704881921866</v>
       </c>
       <c r="C23" t="n">
-        <v>0.05396301665233488</v>
+        <v>0.05396301665233486</v>
       </c>
       <c r="D23" t="n">
         <v>-0.1212726179549302</v>
       </c>
       <c r="E23" t="n">
-        <v>0.09025852031649288</v>
+        <v>0.09025852031649287</v>
       </c>
       <c r="F23" t="n">
-        <v>0.7738333321942777</v>
+        <v>0.7738333321942779</v>
       </c>
       <c r="G23" t="n">
         <v>0.05</v>
@@ -2014,19 +2014,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.01712641609733919</v>
+        <v>-0.01712641609733917</v>
       </c>
       <c r="C24" t="n">
-        <v>0.04898189205297216</v>
+        <v>0.04898189205297218</v>
       </c>
       <c r="D24" t="n">
         <v>-0.1131291604157933</v>
       </c>
       <c r="E24" t="n">
-        <v>0.07887632822111493</v>
+        <v>0.078876328221115</v>
       </c>
       <c r="F24" t="n">
-        <v>0.7266029520031173</v>
+        <v>0.7266029520031178</v>
       </c>
       <c r="G24" t="n">
         <v>0.05</v>
@@ -2039,19 +2039,19 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.01900783443856896</v>
+        <v>0.01900783443856897</v>
       </c>
       <c r="C25" t="n">
-        <v>0.02561343601916736</v>
+        <v>0.02561343601916738</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.03119357767932003</v>
+        <v>-0.03119357767932007</v>
       </c>
       <c r="E25" t="n">
-        <v>0.06920924655645795</v>
+        <v>0.06920924655645801</v>
       </c>
       <c r="F25" t="n">
-        <v>0.4580243001316251</v>
+        <v>0.4580243001316253</v>
       </c>
       <c r="G25" t="n">
         <v>0.05</v>
@@ -2064,19 +2064,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.0114178392397319</v>
+        <v>-0.01141783923973176</v>
       </c>
       <c r="C26" t="n">
         <v>0.03075125430929366</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.07168919016537961</v>
+        <v>-0.07168919016537946</v>
       </c>
       <c r="E26" t="n">
-        <v>0.04885351168591581</v>
+        <v>0.04885351168591594</v>
       </c>
       <c r="F26" t="n">
-        <v>0.7104165557437969</v>
+        <v>0.7104165557438002</v>
       </c>
       <c r="G26" t="n">
         <v>0.05</v>
@@ -2089,19 +2089,19 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.008263771382752895</v>
+        <v>0.008263771382752912</v>
       </c>
       <c r="C27" t="n">
-        <v>0.03117627639559386</v>
+        <v>0.03117627639559385</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.05284060752467729</v>
+        <v>-0.05284060752467724</v>
       </c>
       <c r="E27" t="n">
-        <v>0.06936815029018308</v>
+        <v>0.06936815029018306</v>
       </c>
       <c r="F27" t="n">
-        <v>0.7909586063851299</v>
+        <v>0.7909586063851295</v>
       </c>
       <c r="G27" t="n">
         <v>0.05</v>
@@ -2114,19 +2114,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.0441132339242141</v>
+        <v>0.04411323392421414</v>
       </c>
       <c r="C28" t="n">
-        <v>0.03148338007871244</v>
+        <v>0.03148338007871246</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.0175930571416481</v>
+        <v>-0.01759305714164808</v>
       </c>
       <c r="E28" t="n">
-        <v>0.1058195249900763</v>
+        <v>0.1058195249900764</v>
       </c>
       <c r="F28" t="n">
-        <v>0.1611664122763743</v>
+        <v>0.1611664122763742</v>
       </c>
       <c r="G28" t="n">
         <v>0.05</v>
@@ -2142,16 +2142,16 @@
         <v>-0.0109349089395617</v>
       </c>
       <c r="C29" t="n">
-        <v>0.03231638714325723</v>
+        <v>0.03231638714325727</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.07427386385079912</v>
+        <v>-0.07427386385079919</v>
       </c>
       <c r="E29" t="n">
-        <v>0.05240404597167572</v>
+        <v>0.05240404597167579</v>
       </c>
       <c r="F29" t="n">
-        <v>0.7350840751185987</v>
+        <v>0.7350840751185992</v>
       </c>
       <c r="G29" t="n">
         <v>0.05</v>
@@ -2167,16 +2167,16 @@
         <v>0.2300267851900341</v>
       </c>
       <c r="C30" t="n">
-        <v>0.04275687264023308</v>
+        <v>0.0427568726402331</v>
       </c>
       <c r="D30" t="n">
         <v>0.1462248547236112</v>
       </c>
       <c r="E30" t="n">
-        <v>0.3138287156564569</v>
+        <v>0.313828715656457</v>
       </c>
       <c r="F30" t="n">
-        <v>7.453607464503556e-08</v>
+        <v>7.453607464503609e-08</v>
       </c>
       <c r="G30" t="n">
         <v>0.05</v>
@@ -2185,23 +2185,23 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>baseline_turnover_intention</t>
+          <t>is_new_manager</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.4906715993267194</v>
+        <v>0.009570099507611824</v>
       </c>
       <c r="C31" t="n">
-        <v>0.01020038761332359</v>
+        <v>0.02352815839717277</v>
       </c>
       <c r="D31" t="n">
-        <v>0.4706792069762566</v>
+        <v>-0.03654424357340044</v>
       </c>
       <c r="E31" t="n">
-        <v>0.5106639916771821</v>
+        <v>0.05568444258862409</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>0.6841909551554408</v>
       </c>
       <c r="G31" t="n">
         <v>0.05</v>
@@ -2210,23 +2210,23 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>tenure_months</t>
+          <t>age</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.001002562195601323</v>
+        <v>-0.0008959807646594254</v>
       </c>
       <c r="C32" t="n">
-        <v>0.001411716497337638</v>
+        <v>0.001756049857289153</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.003769475686764128</v>
+        <v>-0.004337775240002869</v>
       </c>
       <c r="E32" t="n">
-        <v>0.001764351295561482</v>
+        <v>0.002545813710684017</v>
       </c>
       <c r="F32" t="n">
-        <v>0.4775971888880661</v>
+        <v>0.6098937492520379</v>
       </c>
       <c r="G32" t="n">
         <v>0.05</v>
@@ -2235,23 +2235,23 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>age</t>
+          <t>tenure_months</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.0008959807646594347</v>
+        <v>-0.001002562195601323</v>
       </c>
       <c r="C33" t="n">
-        <v>0.001756049857289183</v>
+        <v>0.001411716497337632</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.004337775240002936</v>
+        <v>-0.003769475686764117</v>
       </c>
       <c r="E33" t="n">
-        <v>0.002545813710684066</v>
+        <v>0.001764351295561471</v>
       </c>
       <c r="F33" t="n">
-        <v>0.6098937492520402</v>
+        <v>0.4775971888880642</v>
       </c>
       <c r="G33" t="n">
         <v>0.05</v>
@@ -2264,19 +2264,19 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.007701111887135871</v>
+        <v>-0.00770111188713586</v>
       </c>
       <c r="C34" t="n">
-        <v>0.004563797415138302</v>
+        <v>0.00456379741513831</v>
       </c>
       <c r="D34" t="n">
         <v>-0.01664599045354394</v>
       </c>
       <c r="E34" t="n">
-        <v>0.001243766679272195</v>
+        <v>0.00124376667927222</v>
       </c>
       <c r="F34" t="n">
-        <v>0.09151972193447906</v>
+        <v>0.09151972193448007</v>
       </c>
       <c r="G34" t="n">
         <v>0.05</v>
@@ -2285,23 +2285,23 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>is_new_manager</t>
+          <t>tot_span_of_control</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.009570099507611842</v>
+        <v>0.001336822150411826</v>
       </c>
       <c r="C35" t="n">
-        <v>0.02352815839717278</v>
+        <v>0.001449434599930921</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.03654424357340046</v>
+        <v>-0.001504017463399001</v>
       </c>
       <c r="E35" t="n">
-        <v>0.05568444258862414</v>
+        <v>0.004177661764222653</v>
       </c>
       <c r="F35" t="n">
-        <v>0.6841909551554406</v>
+        <v>0.3563690132001174</v>
       </c>
       <c r="G35" t="n">
         <v>0.05</v>
@@ -2310,23 +2310,23 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>tot_span_of_control</t>
+          <t>baseline_turnover_intention</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.001336822150411828</v>
+        <v>0.4906715993267194</v>
       </c>
       <c r="C36" t="n">
-        <v>0.001449434599930922</v>
+        <v>0.01020038761332365</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.001504017463399</v>
+        <v>0.4706792069762565</v>
       </c>
       <c r="E36" t="n">
-        <v>0.004177661764222657</v>
+        <v>0.5106639916771822</v>
       </c>
       <c r="F36" t="n">
-        <v>0.356369013200117</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
         <v>0.05</v>
@@ -2375,13 +2375,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-2.680600179802938</v>
+        <v>-2.680600179802939</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4771933030981325</v>
+        <v>0.4771933030981503</v>
       </c>
       <c r="D2" t="n">
-        <v>1.938181768271168e-08</v>
+        <v>1.938181768273511e-08</v>
       </c>
     </row>
     <row r="3">
@@ -2394,7 +2394,7 @@
         <v>-0.02542074333516161</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1002143663033997</v>
+        <v>0.1002143663033998</v>
       </c>
       <c r="D3" t="n">
         <v>0.79975540801217</v>
@@ -2410,10 +2410,10 @@
         <v>0.2244463748843409</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2335027157442914</v>
+        <v>0.2335027157442915</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3364439424069159</v>
+        <v>0.3364439424069162</v>
       </c>
     </row>
     <row r="5">
@@ -2426,10 +2426,10 @@
         <v>0.8155080917228588</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1734026513921177</v>
+        <v>0.173402651392118</v>
       </c>
       <c r="D5" t="n">
-        <v>2.563995828054277e-06</v>
+        <v>2.563995828054386e-06</v>
       </c>
     </row>
     <row r="6">
@@ -2439,13 +2439,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03527526670387295</v>
+        <v>0.03527526670387308</v>
       </c>
       <c r="C6" t="n">
-        <v>0.191688294691954</v>
+        <v>0.1916882946919544</v>
       </c>
       <c r="D6" t="n">
-        <v>0.853994545471355</v>
+        <v>0.8539945454713548</v>
       </c>
     </row>
     <row r="7">
@@ -2458,10 +2458,10 @@
         <v>0.2773648159307716</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1901447102133382</v>
+        <v>0.1901447102133385</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1446466431125516</v>
+        <v>0.1446466431125523</v>
       </c>
     </row>
     <row r="8">
@@ -2474,10 +2474,10 @@
         <v>0.1036811851537241</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1952515666982443</v>
+        <v>0.1952515666982444</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5954095400432464</v>
+        <v>0.5954095400432469</v>
       </c>
     </row>
     <row r="9">
@@ -2490,10 +2490,10 @@
         <v>0.8738774480300985</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1695280942409136</v>
+        <v>0.1695280942409139</v>
       </c>
       <c r="D9" t="n">
-        <v>2.539495077342701e-07</v>
+        <v>2.539495077342821e-07</v>
       </c>
     </row>
     <row r="10">
@@ -2503,13 +2503,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.04456520772617086</v>
+        <v>-0.0445652077261707</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2604021031716313</v>
+        <v>0.260402103171632</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8641137091517834</v>
+        <v>0.8641137091517843</v>
       </c>
     </row>
     <row r="11">
@@ -2519,13 +2519,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.2737623724798149</v>
+        <v>-0.2737623724798146</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2787881385465057</v>
+        <v>0.2787881385465067</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3261132423877617</v>
+        <v>0.326113242387764</v>
       </c>
     </row>
     <row r="12">
@@ -2535,10 +2535,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.08100487957118127</v>
+        <v>0.08100487957118148</v>
       </c>
       <c r="C12" t="n">
-        <v>0.2596429772097166</v>
+        <v>0.2596429772097172</v>
       </c>
       <c r="D12" t="n">
         <v>0.7550514391424692</v>
@@ -2551,13 +2551,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.03917827337461736</v>
+        <v>0.03917827337461754</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2572958805743769</v>
+        <v>0.2572958805743774</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8789745077123745</v>
+        <v>0.8789745077123743</v>
       </c>
     </row>
     <row r="14">
@@ -2567,13 +2567,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.05296103812307947</v>
+        <v>-0.05296103812307935</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2610089865588713</v>
+        <v>0.2610089865588724</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8392062624375523</v>
+        <v>0.8392062624375534</v>
       </c>
     </row>
     <row r="15">
@@ -2583,13 +2583,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1181322726534159</v>
+        <v>0.1181322726534161</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2572294350577177</v>
+        <v>0.2572294350577187</v>
       </c>
       <c r="D15" t="n">
-        <v>0.646055612898408</v>
+        <v>0.6460556128984086</v>
       </c>
     </row>
     <row r="16">
@@ -2599,13 +2599,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.004000986240379581</v>
+        <v>-0.004000986240379481</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2383903410311186</v>
+        <v>0.2383903410311192</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9866094604655129</v>
+        <v>0.9866094604655132</v>
       </c>
     </row>
     <row r="17">
@@ -2615,13 +2615,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.1057185310395304</v>
+        <v>0.1057185310395306</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2543340222421748</v>
+        <v>0.2543340222421759</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6776529122567303</v>
+        <v>0.677652912256731</v>
       </c>
     </row>
     <row r="18">
@@ -2631,13 +2631,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.1377694895733256</v>
+        <v>-0.1377694895733254</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2636874203313626</v>
+        <v>0.2636874203313636</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6013412201546261</v>
+        <v>0.6013412201546282</v>
       </c>
     </row>
     <row r="19">
@@ -2647,13 +2647,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.02557154094223238</v>
+        <v>-0.02557154094223237</v>
       </c>
       <c r="C19" t="n">
-        <v>0.252759790153811</v>
+        <v>0.2527597901538116</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9194160355966675</v>
+        <v>0.9194160355966677</v>
       </c>
     </row>
     <row r="20">
@@ -2663,13 +2663,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.07344622569376427</v>
+        <v>-0.07344622569376411</v>
       </c>
       <c r="C20" t="n">
-        <v>0.267457860954101</v>
+        <v>0.2674578609541021</v>
       </c>
       <c r="D20" t="n">
-        <v>0.7836169672222772</v>
+        <v>0.7836169672222787</v>
       </c>
     </row>
     <row r="21">
@@ -2679,13 +2679,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.2063167170305059</v>
+        <v>0.2063167170305062</v>
       </c>
       <c r="C21" t="n">
-        <v>0.244289653245072</v>
+        <v>0.2442896532450728</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3983578134719846</v>
+        <v>0.3983578134719854</v>
       </c>
     </row>
     <row r="22">
@@ -2695,13 +2695,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.1704634573362026</v>
+        <v>-0.1704634573362028</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2696748454965904</v>
+        <v>0.269674845496591</v>
       </c>
       <c r="D22" t="n">
-        <v>0.5273167196806361</v>
+        <v>0.5273167196806365</v>
       </c>
     </row>
     <row r="23">
@@ -2711,13 +2711,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.5008110927334757</v>
+        <v>-0.5008110927334755</v>
       </c>
       <c r="C23" t="n">
-        <v>0.287067218044571</v>
+        <v>0.2870672180445716</v>
       </c>
       <c r="D23" t="n">
-        <v>0.08105838975171785</v>
+        <v>0.0810583897517186</v>
       </c>
     </row>
     <row r="24">
@@ -2727,13 +2727,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9366864721074267</v>
+        <v>0.9366864721074268</v>
       </c>
       <c r="C24" t="n">
         <v>0.1483430409733375</v>
       </c>
       <c r="D24" t="n">
-        <v>2.713396260923891e-10</v>
+        <v>2.713396260923871e-10</v>
       </c>
     </row>
     <row r="25">
@@ -2746,10 +2746,10 @@
         <v>-0.5776106069409677</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1143619392421807</v>
+        <v>0.1143619392421806</v>
       </c>
       <c r="D25" t="n">
-        <v>4.401383208103943e-07</v>
+        <v>4.401383208103854e-07</v>
       </c>
     </row>
     <row r="26">
@@ -2759,13 +2759,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.237316144844174</v>
+        <v>0.2373161448441742</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1503781926377478</v>
+        <v>0.1503781926377481</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1145360411757813</v>
+        <v>0.1145360411757815</v>
       </c>
     </row>
     <row r="27">
@@ -2775,13 +2775,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.04350476117998651</v>
+        <v>-0.04350476117998643</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1611879340386412</v>
+        <v>0.1611879340386415</v>
       </c>
       <c r="D27" t="n">
-        <v>0.7872365295400213</v>
+        <v>0.7872365295400221</v>
       </c>
     </row>
     <row r="28">
@@ -2791,13 +2791,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.07514354096975732</v>
+        <v>-0.07514354096975739</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1613683918223567</v>
+        <v>0.1613683918223571</v>
       </c>
       <c r="D28" t="n">
-        <v>0.6414556246120151</v>
+        <v>0.6414556246120158</v>
       </c>
     </row>
     <row r="29">
@@ -2807,29 +2807,29 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.09749293462742097</v>
+        <v>0.09749293462742094</v>
       </c>
       <c r="C29" t="n">
-        <v>0.1543265796290165</v>
+        <v>0.1543265796290169</v>
       </c>
       <c r="D29" t="n">
-        <v>0.5275624553510008</v>
+        <v>0.5275624553510021</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>tenure_months</t>
+          <t>is_new_manager</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.002418133412192873</v>
+        <v>0.2280638724458788</v>
       </c>
       <c r="C30" t="n">
-        <v>0.007135781003458546</v>
+        <v>0.1146565719927948</v>
       </c>
       <c r="D30" t="n">
-        <v>0.7347043603418277</v>
+        <v>0.04668969945129902</v>
       </c>
     </row>
     <row r="31">
@@ -2839,45 +2839,45 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.005012017390962195</v>
+        <v>-0.005012017390962181</v>
       </c>
       <c r="C31" t="n">
-        <v>0.008304876992455039</v>
+        <v>0.008304876992454899</v>
       </c>
       <c r="D31" t="n">
-        <v>0.5461741835341576</v>
+        <v>0.5461741835341518</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>num_direct_reports</t>
+          <t>tenure_months</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.004129656026475419</v>
+        <v>-0.002418133412192865</v>
       </c>
       <c r="C32" t="n">
-        <v>0.02222260881033174</v>
+        <v>0.007135781003458533</v>
       </c>
       <c r="D32" t="n">
-        <v>0.8525770672961279</v>
+        <v>0.7347043603418282</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>is_new_manager</t>
+          <t>num_direct_reports</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.2280638724458785</v>
+        <v>-0.004129656026475429</v>
       </c>
       <c r="C33" t="n">
-        <v>0.1146565719927948</v>
+        <v>0.02222260881033176</v>
       </c>
       <c r="D33" t="n">
-        <v>0.04668969945129923</v>
+        <v>0.8525770672961277</v>
       </c>
     </row>
     <row r="34">
@@ -2887,13 +2887,13 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.006335499136474495</v>
+        <v>0.006335499136474494</v>
       </c>
       <c r="C34" t="n">
-        <v>0.006871422968197181</v>
+        <v>0.006871422968197173</v>
       </c>
       <c r="D34" t="n">
-        <v>0.3565249957666435</v>
+        <v>0.3565249957666431</v>
       </c>
     </row>
   </sheetData>
